--- a/algorithms_data_clean.xlsx
+++ b/algorithms_data_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grachi/vsCode/structure_programming/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93F6F0A-7673-5D46-8B54-E2267E999325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4011D9-D07C-FC40-A7A2-F51D5BF948CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="12260" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Algorithms Data" sheetId="1" r:id="rId1"/>
@@ -506,7 +506,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Max element)</a:t>
+              <a:t>Max element</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1689,6 +1689,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Bubble sort</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2021,6 +2046,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Binary search</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5727,9 +5777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>341194</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>94776</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
